--- a/lessons/chess/excels/remarks_ro.xlsx
+++ b/lessons/chess/excels/remarks_ro.xlsx
@@ -642,7 +642,7 @@
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="J62" authorId="0" shapeId="0">
